--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/114.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/114.xlsx
@@ -426,13 +426,13 @@
         <v>5.992624983377026</v>
       </c>
       <c r="E2">
-        <v>-16.41163114248372</v>
+        <v>-20.79736764943231</v>
       </c>
       <c r="F2">
-        <v>-2.786416856577331</v>
+        <v>-3.351470284681555</v>
       </c>
       <c r="G2">
-        <v>-8.104054414072776</v>
+        <v>-12.69247053150264</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.941994884425373</v>
       </c>
       <c r="E3">
-        <v>-16.12985137583044</v>
+        <v>-20.5713605686575</v>
       </c>
       <c r="F3">
-        <v>-3.099314418901983</v>
+        <v>-3.143110203487992</v>
       </c>
       <c r="G3">
-        <v>-8.526046343418134</v>
+        <v>-11.38382181146536</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.837073634765622</v>
       </c>
       <c r="E4">
-        <v>-17.60411420292356</v>
+        <v>-21.86118770636621</v>
       </c>
       <c r="F4">
-        <v>-2.727538158321147</v>
+        <v>-3.19709325039363</v>
       </c>
       <c r="G4">
-        <v>-7.97425785511457</v>
+        <v>-11.07658001160222</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.690679923994624</v>
       </c>
       <c r="E5">
-        <v>-17.00891875019941</v>
+        <v>-22.21426376779626</v>
       </c>
       <c r="F5">
-        <v>-2.939686363647712</v>
+        <v>-3.316510695181207</v>
       </c>
       <c r="G5">
-        <v>-8.540705439066027</v>
+        <v>-11.87340514908602</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.527033540736788</v>
       </c>
       <c r="E6">
-        <v>-18.2883349261645</v>
+        <v>-21.77903665939307</v>
       </c>
       <c r="F6">
-        <v>-2.65098127132182</v>
+        <v>-3.225444124754444</v>
       </c>
       <c r="G6">
-        <v>-9.402023314200369</v>
+        <v>-12.02136336087266</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.37454279540239</v>
       </c>
       <c r="E7">
-        <v>-18.77770446980339</v>
+        <v>-22.79422090548459</v>
       </c>
       <c r="F7">
-        <v>-2.456056481034263</v>
+        <v>-3.227240025283713</v>
       </c>
       <c r="G7">
-        <v>-9.284200998457708</v>
+        <v>-11.94221483811977</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.253653394381542</v>
       </c>
       <c r="E8">
-        <v>-19.3144871363026</v>
+        <v>-24.50299075906492</v>
       </c>
       <c r="F8">
-        <v>-2.458163847706984</v>
+        <v>-3.188658813498326</v>
       </c>
       <c r="G8">
-        <v>-9.301180786528629</v>
+        <v>-11.99518356674811</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.193335445828143</v>
       </c>
       <c r="E9">
-        <v>-19.63604954711326</v>
+        <v>-23.11454704289116</v>
       </c>
       <c r="F9">
-        <v>-2.345155481514868</v>
+        <v>-3.014936086885422</v>
       </c>
       <c r="G9">
-        <v>-8.741036481283945</v>
+        <v>-11.62887170282775</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.222362257012754</v>
       </c>
       <c r="E10">
-        <v>-20.26147709231261</v>
+        <v>-24.13281517978191</v>
       </c>
       <c r="F10">
-        <v>-2.361849569783486</v>
+        <v>-3.203603389812232</v>
       </c>
       <c r="G10">
-        <v>-8.936928081933699</v>
+        <v>-11.31132086415532</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.35764239387284</v>
       </c>
       <c r="E11">
-        <v>-21.29382878336722</v>
+        <v>-24.97475359576199</v>
       </c>
       <c r="F11">
-        <v>-2.33426410690286</v>
+        <v>-3.082891206774079</v>
       </c>
       <c r="G11">
-        <v>-8.686909061716861</v>
+        <v>-11.48513443660367</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.601028070947246</v>
       </c>
       <c r="E12">
-        <v>-21.24432350551536</v>
+        <v>-26.29443696260328</v>
       </c>
       <c r="F12">
-        <v>-2.453523333516502</v>
+        <v>-2.929449399283916</v>
       </c>
       <c r="G12">
-        <v>-7.632589692188548</v>
+        <v>-10.42574993240028</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.950518456645798</v>
       </c>
       <c r="E13">
-        <v>-22.06626870875158</v>
+        <v>-26.13117641767875</v>
       </c>
       <c r="F13">
-        <v>-2.320626694350572</v>
+        <v>-3.021152984243432</v>
       </c>
       <c r="G13">
-        <v>-7.812670127342743</v>
+        <v>-11.41289833293678</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.397195296635698</v>
       </c>
       <c r="E14">
-        <v>-23.30391424046991</v>
+        <v>-27.29895212393273</v>
       </c>
       <c r="F14">
-        <v>-2.300587658509449</v>
+        <v>-3.00312025425189</v>
       </c>
       <c r="G14">
-        <v>-7.285902742224991</v>
+        <v>-10.58343783752684</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.913040070319287</v>
       </c>
       <c r="E15">
-        <v>-24.2724325619124</v>
+        <v>-28.16100602145488</v>
       </c>
       <c r="F15">
-        <v>-2.329830684563077</v>
+        <v>-2.573516493649024</v>
       </c>
       <c r="G15">
-        <v>-6.485191024278087</v>
+        <v>-9.976876373276037</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.465074893437116</v>
       </c>
       <c r="E16">
-        <v>-24.06037770955522</v>
+        <v>-28.82598073016322</v>
       </c>
       <c r="F16">
-        <v>-1.979978824032137</v>
+        <v>-2.304054376090165</v>
       </c>
       <c r="G16">
-        <v>-5.854114970308977</v>
+        <v>-9.444097037458967</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.024422885906111</v>
       </c>
       <c r="E17">
-        <v>-25.44997618660093</v>
+        <v>-29.34781943243712</v>
       </c>
       <c r="F17">
-        <v>-1.875824877008544</v>
+        <v>-2.285059083176569</v>
       </c>
       <c r="G17">
-        <v>-5.585851533625215</v>
+        <v>-9.095201953620716</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.564599839617674</v>
       </c>
       <c r="E18">
-        <v>-27.08815618734969</v>
+        <v>-30.31241383115195</v>
       </c>
       <c r="F18">
-        <v>-1.897015343539558</v>
+        <v>-2.123195264302143</v>
       </c>
       <c r="G18">
-        <v>-5.122017619209007</v>
+        <v>-8.684393047107015</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>9.052656785814644</v>
       </c>
       <c r="E19">
-        <v>-28.11241096687857</v>
+        <v>-30.75151957754271</v>
       </c>
       <c r="F19">
-        <v>-1.435240278114168</v>
+        <v>-1.942409877212971</v>
       </c>
       <c r="G19">
-        <v>-4.472710390955132</v>
+        <v>-8.012802536828305</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>9.467827786110886</v>
       </c>
       <c r="E20">
-        <v>-28.85099602058159</v>
+        <v>-31.35609802841075</v>
       </c>
       <c r="F20">
-        <v>-1.421206905943341</v>
+        <v>-1.944046731200902</v>
       </c>
       <c r="G20">
-        <v>-3.869005927504717</v>
+        <v>-7.92224918469262</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>9.798996479895912</v>
       </c>
       <c r="E21">
-        <v>-29.0704458709933</v>
+        <v>-32.26925349087246</v>
       </c>
       <c r="F21">
-        <v>-1.127336114493591</v>
+        <v>-1.72180901090824</v>
       </c>
       <c r="G21">
-        <v>-3.884552249357134</v>
+        <v>-7.341503354557051</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>10.03955734848836</v>
       </c>
       <c r="E22">
-        <v>-29.29053423624009</v>
+        <v>-32.37298950920317</v>
       </c>
       <c r="F22">
-        <v>-1.283048477034828</v>
+        <v>-1.728560205241056</v>
       </c>
       <c r="G22">
-        <v>-3.249784937111738</v>
+        <v>-7.109599639531104</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>10.18000225963026</v>
       </c>
       <c r="E23">
-        <v>-31.01179135689656</v>
+        <v>-33.37355357696093</v>
       </c>
       <c r="F23">
-        <v>-0.8549771961271418</v>
+        <v>-1.728728363823824</v>
       </c>
       <c r="G23">
-        <v>-3.160052600269792</v>
+        <v>-7.435708238422551</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>10.22316771997894</v>
       </c>
       <c r="E24">
-        <v>-31.15258614226904</v>
+        <v>-34.11927550570004</v>
       </c>
       <c r="F24">
-        <v>-0.6735481675659941</v>
+        <v>-1.519303830517664</v>
       </c>
       <c r="G24">
-        <v>-3.028004870344882</v>
+        <v>-6.403453654913481</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>10.17839420268203</v>
       </c>
       <c r="E25">
-        <v>-31.03588057438036</v>
+        <v>-33.21810012122562</v>
       </c>
       <c r="F25">
-        <v>-0.8580322151086665</v>
+        <v>-1.358096078626255</v>
       </c>
       <c r="G25">
-        <v>-3.271157819113272</v>
+        <v>-7.088292968440355</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.05280860277906</v>
       </c>
       <c r="E26">
-        <v>-31.15475075284471</v>
+        <v>-33.95493491972468</v>
       </c>
       <c r="F26">
-        <v>-0.7606195220090558</v>
+        <v>-1.484295367340551</v>
       </c>
       <c r="G26">
-        <v>-3.217179374095456</v>
+        <v>-7.062030410677316</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>9.852033304288209</v>
       </c>
       <c r="E27">
-        <v>-31.37215826147895</v>
+        <v>-33.77893577741657</v>
       </c>
       <c r="F27">
-        <v>-0.8589724121108439</v>
+        <v>-1.434383746219673</v>
       </c>
       <c r="G27">
-        <v>-3.534193904390525</v>
+        <v>-7.294324770076897</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.586030993177756</v>
       </c>
       <c r="E28">
-        <v>-30.99848217178802</v>
+        <v>-34.60898242065251</v>
       </c>
       <c r="F28">
-        <v>-0.8856359020721544</v>
+        <v>-1.304467572969015</v>
       </c>
       <c r="G28">
-        <v>-2.734703777747612</v>
+        <v>-7.952143410912239</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>9.272893883913595</v>
       </c>
       <c r="E29">
-        <v>-31.30421756594188</v>
+        <v>-33.45777640079259</v>
       </c>
       <c r="F29">
-        <v>-0.6109086813011011</v>
+        <v>-1.276192080041857</v>
       </c>
       <c r="G29">
-        <v>-3.966491561999635</v>
+        <v>-7.55595056295442</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.921337124128904</v>
       </c>
       <c r="E30">
-        <v>-30.82137355334803</v>
+        <v>-34.93680997525279</v>
       </c>
       <c r="F30">
-        <v>-0.6368282973346977</v>
+        <v>-1.561463589483145</v>
       </c>
       <c r="G30">
-        <v>-3.090289474120731</v>
+        <v>-7.473809307034023</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>8.539487867231903</v>
       </c>
       <c r="E31">
-        <v>-31.60400480948666</v>
+        <v>-33.72089206182326</v>
       </c>
       <c r="F31">
-        <v>-0.8762844624619508</v>
+        <v>-1.456196316670189</v>
       </c>
       <c r="G31">
-        <v>-3.752041043056726</v>
+        <v>-7.690196495117406</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.13974849500196</v>
       </c>
       <c r="E32">
-        <v>-30.70485365289367</v>
+        <v>-32.74392134364545</v>
       </c>
       <c r="F32">
-        <v>-0.8935211313794029</v>
+        <v>-1.536496595962768</v>
       </c>
       <c r="G32">
-        <v>-4.167501266053104</v>
+        <v>-8.143089056526321</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>7.738097027943604</v>
       </c>
       <c r="E33">
-        <v>-30.67456721873037</v>
+        <v>-33.14217799025003</v>
       </c>
       <c r="F33">
-        <v>-0.7395582807928783</v>
+        <v>-1.660586861269537</v>
       </c>
       <c r="G33">
-        <v>-4.053542356954772</v>
+        <v>-7.766709823621041</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>7.340176897095639</v>
       </c>
       <c r="E34">
-        <v>-29.69869239126243</v>
+        <v>-32.51176233093123</v>
       </c>
       <c r="F34">
-        <v>-0.7058072793332153</v>
+        <v>-1.626014119346296</v>
       </c>
       <c r="G34">
-        <v>-4.609005550806927</v>
+        <v>-7.427004814199807</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.951838529015641</v>
       </c>
       <c r="E35">
-        <v>-29.77978151108078</v>
+        <v>-31.45479611940793</v>
       </c>
       <c r="F35">
-        <v>-0.6970588911922497</v>
+        <v>-1.416864604017866</v>
       </c>
       <c r="G35">
-        <v>-4.288597711334104</v>
+        <v>-7.857140685571773</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.584557664911254</v>
       </c>
       <c r="E36">
-        <v>-29.60783535300953</v>
+        <v>-32.56635082085668</v>
       </c>
       <c r="F36">
-        <v>-0.673644258184719</v>
+        <v>-0.9637534332583562</v>
       </c>
       <c r="G36">
-        <v>-4.962121580207748</v>
+        <v>-7.871541558667603</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.246599709313924</v>
       </c>
       <c r="E37">
-        <v>-28.67045029036979</v>
+        <v>-31.65121641525363</v>
       </c>
       <c r="F37">
-        <v>-0.6929170541782522</v>
+        <v>-1.168492720534282</v>
       </c>
       <c r="G37">
-        <v>-4.716899540477314</v>
+        <v>-8.337580296412964</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.937413024128755</v>
       </c>
       <c r="E38">
-        <v>-26.95807124300535</v>
+        <v>-30.00102916567353</v>
       </c>
       <c r="F38">
-        <v>-0.6443109400841857</v>
+        <v>-1.333018083873903</v>
       </c>
       <c r="G38">
-        <v>-5.443266337248805</v>
+        <v>-8.618844245429445</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.65613118706061</v>
       </c>
       <c r="E39">
-        <v>-26.86622926165579</v>
+        <v>-29.21765297556064</v>
       </c>
       <c r="F39">
-        <v>-0.2701763175075805</v>
+        <v>-1.154378996725384</v>
       </c>
       <c r="G39">
-        <v>-5.317356358753704</v>
+        <v>-8.929029120276999</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.408070544333745</v>
       </c>
       <c r="E40">
-        <v>-26.49723108561478</v>
+        <v>-29.33017649770323</v>
       </c>
       <c r="F40">
-        <v>-0.360115479899134</v>
+        <v>-1.191440154326634</v>
       </c>
       <c r="G40">
-        <v>-5.421701443605992</v>
+        <v>-8.164644018532517</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.18989365970248</v>
       </c>
       <c r="E41">
-        <v>-25.92172543787598</v>
+        <v>-29.26921870908598</v>
       </c>
       <c r="F41">
-        <v>-0.02414871377391894</v>
+        <v>-0.975942031223148</v>
       </c>
       <c r="G41">
-        <v>-5.207992486863881</v>
+        <v>-8.979253406653282</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.993468279222463</v>
       </c>
       <c r="E42">
-        <v>-25.73952681465137</v>
+        <v>-28.86090885018439</v>
       </c>
       <c r="F42">
-        <v>-0.1975384366908975</v>
+        <v>-1.012176478156404</v>
       </c>
       <c r="G42">
-        <v>-5.863748657828256</v>
+        <v>-8.528218061291897</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.810729541995054</v>
       </c>
       <c r="E43">
-        <v>-24.80233647639395</v>
+        <v>-27.91335283492341</v>
       </c>
       <c r="F43">
-        <v>-0.4714729098574716</v>
+        <v>-0.9487831775549636</v>
       </c>
       <c r="G43">
-        <v>-5.773261516603357</v>
+        <v>-8.460355188282376</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.639962965593213</v>
       </c>
       <c r="E44">
-        <v>-24.14839765884231</v>
+        <v>-27.76975945261419</v>
       </c>
       <c r="F44">
-        <v>0.08990753718273939</v>
+        <v>-0.853724704614109</v>
       </c>
       <c r="G44">
-        <v>-5.646543764996673</v>
+        <v>-8.804714824731827</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.471477024753435</v>
       </c>
       <c r="E45">
-        <v>-23.42862841464116</v>
+        <v>-26.15751855098137</v>
       </c>
       <c r="F45">
-        <v>-0.2266431253882581</v>
+        <v>-0.7686281780593214</v>
       </c>
       <c r="G45">
-        <v>-5.363968839946643</v>
+        <v>-8.424429148090205</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.295595584129132</v>
       </c>
       <c r="E46">
-        <v>-22.20107685148592</v>
+        <v>-26.94039660895341</v>
       </c>
       <c r="F46">
-        <v>0.075481518862986</v>
+        <v>-0.6102377037048335</v>
       </c>
       <c r="G46">
-        <v>-6.192820194977352</v>
+        <v>-9.477937433961397</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.106050126713404</v>
       </c>
       <c r="E47">
-        <v>-21.65434965606587</v>
+        <v>-25.45895615055814</v>
       </c>
       <c r="F47">
-        <v>0.3073448683761788</v>
+        <v>-0.4118751886956583</v>
       </c>
       <c r="G47">
-        <v>-6.700810165796359</v>
+        <v>-9.242044511560628</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.89954086062134</v>
       </c>
       <c r="E48">
-        <v>-20.20726220149279</v>
+        <v>-25.58803124519876</v>
       </c>
       <c r="F48">
-        <v>0.4785344474713218</v>
+        <v>-0.3910881370898076</v>
       </c>
       <c r="G48">
-        <v>-6.044120420989907</v>
+        <v>-8.412014602317939</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.669469516709404</v>
       </c>
       <c r="E49">
-        <v>-21.33694891286826</v>
+        <v>-24.37541458932083</v>
       </c>
       <c r="F49">
-        <v>0.4527465418547704</v>
+        <v>-0.491468042226246</v>
       </c>
       <c r="G49">
-        <v>-5.792028999265486</v>
+        <v>-8.54196344637095</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.40978748625285</v>
       </c>
       <c r="E50">
-        <v>-19.51025306765419</v>
+        <v>-23.70904058214412</v>
       </c>
       <c r="F50">
-        <v>0.4564385753690479</v>
+        <v>-0.5456747483306401</v>
       </c>
       <c r="G50">
-        <v>-6.157989945358679</v>
+        <v>-8.735895204061457</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.120370746796339</v>
       </c>
       <c r="E51">
-        <v>-19.25132850931762</v>
+        <v>-23.28564637632297</v>
       </c>
       <c r="F51">
-        <v>0.327051728888779</v>
+        <v>-0.317187824351258</v>
       </c>
       <c r="G51">
-        <v>-5.531985647155734</v>
+        <v>-9.15327885401615</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.802392330495612</v>
       </c>
       <c r="E52">
-        <v>-18.63238573889725</v>
+        <v>-22.48903345668566</v>
       </c>
       <c r="F52">
-        <v>0.5347134963617816</v>
+        <v>-0.3425358668769229</v>
       </c>
       <c r="G52">
-        <v>-5.802808135541352</v>
+        <v>-9.349541235766303</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.4581631612248</v>
       </c>
       <c r="E53">
-        <v>-18.36127052853203</v>
+        <v>-21.35130870394658</v>
       </c>
       <c r="F53">
-        <v>0.4405214957242554</v>
+        <v>-0.3199744522942756</v>
       </c>
       <c r="G53">
-        <v>-6.591767416823844</v>
+        <v>-9.592790190355332</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.090859647337526</v>
       </c>
       <c r="E54">
-        <v>-17.11882481436557</v>
+        <v>-21.70735997279966</v>
       </c>
       <c r="F54">
-        <v>0.5482432211517059</v>
+        <v>-0.05883742713355104</v>
       </c>
       <c r="G54">
-        <v>-5.908477438609349</v>
+        <v>-9.565163687830115</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.711880711609767</v>
       </c>
       <c r="E55">
-        <v>-16.86010403735935</v>
+        <v>-21.66625501423204</v>
       </c>
       <c r="F55">
-        <v>0.4312230716278309</v>
+        <v>-0.4526283798111856</v>
       </c>
       <c r="G55">
-        <v>-6.535478211019615</v>
+        <v>-8.825740099451737</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.331960772333493</v>
       </c>
       <c r="E56">
-        <v>-15.09379086456356</v>
+        <v>-21.08022972137342</v>
       </c>
       <c r="F56">
-        <v>0.5495363026674759</v>
+        <v>-0.3667217099364601</v>
       </c>
       <c r="G56">
-        <v>-6.451165237225458</v>
+        <v>-9.468595074449574</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9625254708641575</v>
       </c>
       <c r="E57">
-        <v>-14.98088695060432</v>
+        <v>-20.47918800870537</v>
       </c>
       <c r="F57">
-        <v>0.6222363110393689</v>
+        <v>0.02116546826142241</v>
       </c>
       <c r="G57">
-        <v>-6.146379862152456</v>
+        <v>-9.49677443807985</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.6152999196379095</v>
       </c>
       <c r="E58">
-        <v>-15.0531976235588</v>
+        <v>-20.20248466141469</v>
       </c>
       <c r="F58">
-        <v>0.5097108830430841</v>
+        <v>-0.5425576017939056</v>
       </c>
       <c r="G58">
-        <v>-6.247649450198761</v>
+        <v>-10.0407136229098</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.305938123018429</v>
       </c>
       <c r="E59">
-        <v>-15.02762985931149</v>
+        <v>-19.49879602841478</v>
       </c>
       <c r="F59">
-        <v>0.4775097569940588</v>
+        <v>-0.5827673838931964</v>
       </c>
       <c r="G59">
-        <v>-7.237366834073736</v>
+        <v>-10.32175576537515</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.04535664979745377</v>
       </c>
       <c r="E60">
-        <v>-14.49542548003404</v>
+        <v>-18.60305934122358</v>
       </c>
       <c r="F60">
-        <v>0.03952126154005666</v>
+        <v>-0.6259435496619121</v>
       </c>
       <c r="G60">
-        <v>-6.574042756006586</v>
+        <v>-10.05568059929285</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.1583353998386224</v>
       </c>
       <c r="E61">
-        <v>-13.01499487134248</v>
+        <v>-18.335861260875</v>
       </c>
       <c r="F61">
-        <v>0.1498813371454236</v>
+        <v>-0.6116807197205103</v>
       </c>
       <c r="G61">
-        <v>-6.976658062310591</v>
+        <v>-9.55918815313173</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.2984155777613762</v>
       </c>
       <c r="E62">
-        <v>-13.46579540185805</v>
+        <v>-18.71286125048756</v>
       </c>
       <c r="F62">
-        <v>-0.3013038794025775</v>
+        <v>-0.7822896132662909</v>
       </c>
       <c r="G62">
-        <v>-6.643349026871229</v>
+        <v>-9.988029601197841</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.370944090788614</v>
       </c>
       <c r="E63">
-        <v>-13.58718114763365</v>
+        <v>-17.78653019290054</v>
       </c>
       <c r="F63">
-        <v>0.03317099703019565</v>
+        <v>-1.000454251039388</v>
       </c>
       <c r="G63">
-        <v>-7.398593712381782</v>
+        <v>-10.03143416376322</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.3784084715029663</v>
       </c>
       <c r="E64">
-        <v>-13.20159517130254</v>
+        <v>-16.83792357166978</v>
       </c>
       <c r="F64">
-        <v>-0.4444151170124285</v>
+        <v>-1.011046585018986</v>
       </c>
       <c r="G64">
-        <v>-7.12006427398074</v>
+        <v>-10.53137288783072</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.3256365076796565</v>
       </c>
       <c r="E65">
-        <v>-12.36544867357827</v>
+        <v>-18.27386645170999</v>
       </c>
       <c r="F65">
-        <v>-0.7968274611854221</v>
+        <v>-1.291576519446649</v>
       </c>
       <c r="G65">
-        <v>-7.687458673956429</v>
+        <v>-10.88724329112022</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.2184771866476287</v>
       </c>
       <c r="E66">
-        <v>-12.27981975856723</v>
+        <v>-16.51095869136796</v>
       </c>
       <c r="F66">
-        <v>-0.6954303208783459</v>
+        <v>-1.289988539135483</v>
       </c>
       <c r="G66">
-        <v>-7.338268951565182</v>
+        <v>-10.70354111914606</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.06598453507856568</v>
       </c>
       <c r="E67">
-        <v>-12.35065414899521</v>
+        <v>-17.53833358948814</v>
       </c>
       <c r="F67">
-        <v>-1.07604194817744</v>
+        <v>-1.449009401083501</v>
       </c>
       <c r="G67">
-        <v>-7.317680668856455</v>
+        <v>-10.35073959157147</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.120284922875805</v>
       </c>
       <c r="E68">
-        <v>-12.22545089963114</v>
+        <v>-16.21563425895774</v>
       </c>
       <c r="F68">
-        <v>-1.06316746200313</v>
+        <v>-1.356894945892196</v>
       </c>
       <c r="G68">
-        <v>-7.926529720074897</v>
+        <v>-10.34738600894019</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.331509315246395</v>
       </c>
       <c r="E69">
-        <v>-10.8993008719069</v>
+        <v>-16.73945643284699</v>
       </c>
       <c r="F69">
-        <v>-1.257222466517748</v>
+        <v>-1.448484216150126</v>
       </c>
       <c r="G69">
-        <v>-7.65238344396785</v>
+        <v>-10.32957858448445</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.5598413222868271</v>
       </c>
       <c r="E70">
-        <v>-11.50173735456931</v>
+        <v>-16.71270220840968</v>
       </c>
       <c r="F70">
-        <v>-1.257946459627795</v>
+        <v>-1.723605739804912</v>
       </c>
       <c r="G70">
-        <v>-7.102889163723001</v>
+        <v>-10.01315995238645</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.797024348815682</v>
       </c>
       <c r="E71">
-        <v>-11.20264976025872</v>
+        <v>-15.83436844682995</v>
       </c>
       <c r="F71">
-        <v>-1.396051873022529</v>
+        <v>-1.863759705786769</v>
       </c>
       <c r="G71">
-        <v>-7.175588743765396</v>
+        <v>-9.787334398970604</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.035327396925948</v>
       </c>
       <c r="E72">
-        <v>-10.63348850460467</v>
+        <v>-16.12361566712188</v>
       </c>
       <c r="F72">
-        <v>-1.424082169198458</v>
+        <v>-2.148600464178601</v>
       </c>
       <c r="G72">
-        <v>-7.639217404358169</v>
+        <v>-9.758324088409969</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.269849305747122</v>
       </c>
       <c r="E73">
-        <v>-11.96238731605157</v>
+        <v>-15.82587302959156</v>
       </c>
       <c r="F73">
-        <v>-1.626215412625177</v>
+        <v>-1.792024745439137</v>
       </c>
       <c r="G73">
-        <v>-7.223333431532765</v>
+        <v>-10.15896299902703</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.495522120635588</v>
       </c>
       <c r="E74">
-        <v>-11.36527179034817</v>
+        <v>-16.57029528629047</v>
       </c>
       <c r="F74">
-        <v>-1.741464512641866</v>
+        <v>-1.990252236561656</v>
       </c>
       <c r="G74">
-        <v>-6.941311367587792</v>
+        <v>-9.8020696371659</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.706670734648633</v>
       </c>
       <c r="E75">
-        <v>-11.68359634224335</v>
+        <v>-17.32572626330202</v>
       </c>
       <c r="F75">
-        <v>-1.433904949860855</v>
+        <v>-2.528454963671537</v>
       </c>
       <c r="G75">
-        <v>-6.152338844123143</v>
+        <v>-9.259871799289604</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.899651726699067</v>
       </c>
       <c r="E76">
-        <v>-11.9152368446837</v>
+        <v>-17.5688962605659</v>
       </c>
       <c r="F76">
-        <v>-1.889999900005249</v>
+        <v>-2.299780828659122</v>
       </c>
       <c r="G76">
-        <v>-6.134147396384848</v>
+        <v>-9.386870947267125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.071961006259904</v>
       </c>
       <c r="E77">
-        <v>-11.59022373667919</v>
+        <v>-18.23792848198512</v>
       </c>
       <c r="F77">
-        <v>-2.142036480878818</v>
+        <v>-2.18192402805842</v>
       </c>
       <c r="G77">
-        <v>-5.515651415464969</v>
+        <v>-8.986910698485616</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.221562952853816</v>
       </c>
       <c r="E78">
-        <v>-12.171050341377</v>
+        <v>-17.85483769483223</v>
       </c>
       <c r="F78">
-        <v>-1.548290062676424</v>
+        <v>-2.425922960022625</v>
       </c>
       <c r="G78">
-        <v>-6.245044050859355</v>
+        <v>-9.33415382009977</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.345422041827466</v>
       </c>
       <c r="E79">
-        <v>-13.41979063441412</v>
+        <v>-17.38106874414976</v>
       </c>
       <c r="F79">
-        <v>-2.302883892950009</v>
+        <v>-2.411839885807631</v>
       </c>
       <c r="G79">
-        <v>-5.039780357467972</v>
+        <v>-8.582458039407316</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.443744254098639</v>
       </c>
       <c r="E80">
-        <v>-13.59852497502287</v>
+        <v>-17.87137568190824</v>
       </c>
       <c r="F80">
-        <v>-1.788772575015746</v>
+        <v>-2.671982041717593</v>
       </c>
       <c r="G80">
-        <v>-5.336249642146325</v>
+        <v>-8.333024985750928</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.516632372073723</v>
       </c>
       <c r="E81">
-        <v>-13.99396038232066</v>
+        <v>-18.57666286623287</v>
       </c>
       <c r="F81">
-        <v>-2.405861558261627</v>
+        <v>-2.189485365711173</v>
       </c>
       <c r="G81">
-        <v>-4.668512606875327</v>
+        <v>-8.155348006658244</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.563844650736018</v>
       </c>
       <c r="E82">
-        <v>-14.57993586196518</v>
+        <v>-19.66759489705069</v>
       </c>
       <c r="F82">
-        <v>-2.289597708176508</v>
+        <v>-2.410508699391332</v>
       </c>
       <c r="G82">
-        <v>-5.10406453074954</v>
+        <v>-7.570980439702711</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.584214046831826</v>
       </c>
       <c r="E83">
-        <v>-14.76781772006942</v>
+        <v>-20.11024870282646</v>
       </c>
       <c r="F83">
-        <v>-2.198143461805234</v>
+        <v>-2.819028024490742</v>
       </c>
       <c r="G83">
-        <v>-4.199749290151144</v>
+        <v>-8.088233316940599</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.577812588914907</v>
       </c>
       <c r="E84">
-        <v>-16.52008356649342</v>
+        <v>-20.72500263478974</v>
       </c>
       <c r="F84">
-        <v>-2.420964352749467</v>
+        <v>-2.541800790898039</v>
       </c>
       <c r="G84">
-        <v>-4.470581710173381</v>
+        <v>-7.603539655081443</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.545689373612973</v>
       </c>
       <c r="E85">
-        <v>-16.56737442055552</v>
+        <v>-22.28060138353462</v>
       </c>
       <c r="F85">
-        <v>-2.223239680640448</v>
+        <v>-2.852207452442473</v>
       </c>
       <c r="G85">
-        <v>-4.078106604856163</v>
+        <v>-7.385924254602991</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.487586907558254</v>
       </c>
       <c r="E86">
-        <v>-18.07286560440553</v>
+        <v>-22.87778936482214</v>
       </c>
       <c r="F86">
-        <v>-2.775494832371419</v>
+        <v>-2.882336831617097</v>
       </c>
       <c r="G86">
-        <v>-4.360602076813253</v>
+        <v>-7.446040451050616</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.403271275537794</v>
       </c>
       <c r="E87">
-        <v>-19.04739321085619</v>
+        <v>-24.55450215090217</v>
       </c>
       <c r="F87">
-        <v>-2.675238353977998</v>
+        <v>-2.89844360739713</v>
       </c>
       <c r="G87">
-        <v>-3.512569420928006</v>
+        <v>-7.064864237658932</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.293566235009271</v>
       </c>
       <c r="E88">
-        <v>-20.33681278590422</v>
+        <v>-23.94169546276219</v>
       </c>
       <c r="F88">
-        <v>-2.655710420824402</v>
+        <v>-3.128445615356233</v>
       </c>
       <c r="G88">
-        <v>-4.023873247831823</v>
+        <v>-7.910361015661097</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.161470008342701</v>
       </c>
       <c r="E89">
-        <v>-21.93299571870584</v>
+        <v>-25.77233560883694</v>
       </c>
       <c r="F89">
-        <v>-2.617854858883868</v>
+        <v>-3.04621772511734</v>
       </c>
       <c r="G89">
-        <v>-3.662500717856059</v>
+        <v>-6.823512225663905</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.009066042028896</v>
       </c>
       <c r="E90">
-        <v>-22.921987271137</v>
+        <v>-26.35783107023666</v>
       </c>
       <c r="F90">
-        <v>-2.626257817817866</v>
+        <v>-3.092341222105216</v>
       </c>
       <c r="G90">
-        <v>-3.315505887157349</v>
+        <v>-7.457196989517961</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.83880615490219</v>
       </c>
       <c r="E91">
-        <v>-24.56180205100253</v>
+        <v>-28.00432987773751</v>
       </c>
       <c r="F91">
-        <v>-2.899258720921485</v>
+        <v>-3.497462584118342</v>
       </c>
       <c r="G91">
-        <v>-3.241839627817487</v>
+        <v>-7.213239578183527</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.654759098338468</v>
       </c>
       <c r="E92">
-        <v>-26.07579318056494</v>
+        <v>-30.96677153254931</v>
       </c>
       <c r="F92">
-        <v>-2.743981251266718</v>
+        <v>-3.36613652954812</v>
       </c>
       <c r="G92">
-        <v>-3.722802304853883</v>
+        <v>-7.047358072847266</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.461713642144617</v>
       </c>
       <c r="E93">
-        <v>-28.16419859563029</v>
+        <v>-31.9221912429246</v>
       </c>
       <c r="F93">
-        <v>-3.134903567628458</v>
+        <v>-3.879711893772771</v>
       </c>
       <c r="G93">
-        <v>-3.590701606200345</v>
+        <v>-7.62177082936621</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.263516433269614</v>
       </c>
       <c r="E94">
-        <v>-30.09201979390965</v>
+        <v>-33.08119303078873</v>
       </c>
       <c r="F94">
-        <v>-3.07510620992257</v>
+        <v>-4.174827721428929</v>
       </c>
       <c r="G94">
-        <v>-4.51046716283052</v>
+        <v>-7.873170347072924</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.063188498530307</v>
       </c>
       <c r="E95">
-        <v>-32.25106713925766</v>
+        <v>-33.80609982875158</v>
       </c>
       <c r="F95">
-        <v>-3.259389792553764</v>
+        <v>-3.689836002805277</v>
       </c>
       <c r="G95">
-        <v>-4.517204123002936</v>
+        <v>-7.833142540957597</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.8664123808720393</v>
       </c>
       <c r="E96">
-        <v>-33.26884846519258</v>
+        <v>-36.05021002985967</v>
       </c>
       <c r="F96">
-        <v>-3.490745352849041</v>
+        <v>-3.9277149563976</v>
       </c>
       <c r="G96">
-        <v>-5.025644328015284</v>
+        <v>-7.987781433642493</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.6783230174643035</v>
       </c>
       <c r="E97">
-        <v>-34.60480943185444</v>
+        <v>-38.19580101469388</v>
       </c>
       <c r="F97">
-        <v>-3.345991462679439</v>
+        <v>-4.180676823660097</v>
       </c>
       <c r="G97">
-        <v>-5.123616612704476</v>
+        <v>-7.970675844841079</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.5032907664502139</v>
       </c>
       <c r="E98">
-        <v>-37.75379704493822</v>
+        <v>-39.22369215885093</v>
       </c>
       <c r="F98">
-        <v>-3.562494395442521</v>
+        <v>-4.700582571576941</v>
       </c>
       <c r="G98">
-        <v>-5.498264430292718</v>
+        <v>-8.734806034579035</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.3444215994957029</v>
       </c>
       <c r="E99">
-        <v>-39.98570527283263</v>
+        <v>-40.89766521815632</v>
       </c>
       <c r="F99">
-        <v>-3.835242646488286</v>
+        <v>-4.689606703489848</v>
       </c>
       <c r="G99">
-        <v>-6.282999455467099</v>
+        <v>-8.8977709492952</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.2068213108708172</v>
       </c>
       <c r="E100">
-        <v>-41.63414000297176</v>
+        <v>-44.0809605503222</v>
       </c>
       <c r="F100">
-        <v>-3.660045425898399</v>
+        <v>-4.963834418717013</v>
       </c>
       <c r="G100">
-        <v>-5.567802439345108</v>
+        <v>-9.526370715200935</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.0933162322654892</v>
       </c>
       <c r="E101">
-        <v>-43.46977052740296</v>
+        <v>-45.00793238698132</v>
       </c>
       <c r="F101">
-        <v>-4.162367418956019</v>
+        <v>-4.609546650744082</v>
       </c>
       <c r="G101">
-        <v>-6.117098086857601</v>
+        <v>-9.259818830560976</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.00436001661952671</v>
       </c>
       <c r="E102">
-        <v>-46.08188716874439</v>
+        <v>-48.20981936918569</v>
       </c>
       <c r="F102">
-        <v>-4.052361056231647</v>
+        <v>-5.136621918532157</v>
       </c>
       <c r="G102">
-        <v>-6.696023116946572</v>
+        <v>-10.00277808157529</v>
       </c>
     </row>
   </sheetData>
